--- a/gl_claim_v3.xlsx
+++ b/gl_claim_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Himanshu Bist\OneDrive\Desktop\Testing-Projects\Test4\python-files-objections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF1F809F-C82C-4F5D-AE3F-7BEC133EB572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B34A722-3B37-49B8-A2ED-0F06D1ED10A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,11 +74,28 @@
     <t>0.96</t>
   </si>
   <si>
+    <t>Taxonomy</t>
+  </si>
+  <si>
+    <t>Loss_Desc</t>
+  </si>
+  <si>
+    <t>Claim_Notes</t>
+  </si>
+  <si>
+    <t>Claimant (female, age 43) reports that on the evening of March 14th she entered the insured's casual dining restaurant and slipped on a wet floor near the host stand, approx. 6 feet inside the main entrance.
+She states there was no wet floor sign posted and the lighting in the area was dim. Claimant fell backward, striking her right wrist and lower back on the tile floor. She was assisted by restaurant staff and transported via ambulance to St. Mary's Regional Medical Center. ER report confirms a displaced fracture of the distal radius (right wrist) and lumbar strain. Claimant underwent outpatient surgery and is currently in physical therapy (8 sessions completed, 6 remaining). Claimant is employed as a dental hygienist and has been unable to work since the incident — lost wages claim expected. Insured acknowledges the floor had been mopped 20 minutes prior; no incident report was filed at time of loss. Security footage has been requested and is pending review.</t>
+  </si>
+  <si>
+    <t>Claimant sustained displaced distal radius fracture + lumbar strain confirmed by ER. Physical injury to person = Bodily Injury class. Injury occurred on insured's active premises (restaurant entrance). Floor mopped 20 min prior by staff — ongoing ops negligence. No wet floor sign posted (insured acknowledged).</t>
+  </si>
+  <si>
     <t>▶ Bodily Injury
     ├─ Prem/Ops Liability
     │      • Animal/Dog Bite
     │      • Loading/Unloading
     │      • Object Fell on Patron
+    │      • Wet Floors
     ├─ Completed Operations
     │      • Construction
     │      • Snow Removal
@@ -95,36 +112,11 @@
     │      • Water Damage  •  Collapse  •  HVAC
     └─ Mobile Equipment
            • Other
-▶ Food Related
-    ├─ Food Borne Illness
-    │      • Employee Error  •  Supply Chain 
-    └─ Food Borne Allergen
-           • Employee Error  •  Improper Label
-▶ Slip and Fall
-    └─ Injury Slip or Fall
-           • Wet Floors  •  Ice/Snow/Rain
 ▶ Other Liability
     ├─ Cyber Attack or ID Theft
     │      • Cyber Attack  •  ID Theft
     └─ Sports Liability
            • Equine  •  Skiing/Snowboarding</t>
-  </si>
-  <si>
-    <t>Taxonomy</t>
-  </si>
-  <si>
-    <t>Claimant sustained displaced distal radius fracture + lumbar strain confirmed by ER. Physical injury to person = Bodily Injury class. Injury occurred on insured's active premises (restaurant entrance). Floor mopped 20 min prior by staff — ongoing ops negligence. No wet floor sign posted (insured acknowledged). Claim explicitly states 'slipped on a wet floor'; insured confirmed mopping 20 min prior; no signage present. Direct keyword +
- causal chain match to 'Wet Floors' node.</t>
-  </si>
-  <si>
-    <t>Loss_Desc</t>
-  </si>
-  <si>
-    <t>Claim_Notes</t>
-  </si>
-  <si>
-    <t>Claimant (female, age 43) reports that on the evening of March 14th she entered the insured's casual dining restaurant and slipped on a wet floor near the host stand, approx. 6 feet inside the main entrance.
-She states there was no wet floor sign posted and the lighting in the area was dim. Claimant fell backward, striking her right wrist and lower back on the tile floor. She was assisted by restaurant staff and transported via ambulance to St. Mary's Regional Medical Center. ER report confirms a displaced fracture of the distal radius (right wrist) and lumbar strain. Claimant underwent outpatient surgery and is currently in physical therapy (8 sessions completed, 6 remaining). Claimant is employed as a dental hygienist and has been unable to work since the incident — lost wages claim expected. Insured acknowledges the floor had been mopped 20 minutes prior; no incident report was filed at time of loss. Security footage has been requested and is pending review.</t>
   </si>
 </sst>
 </file>
@@ -140,16 +132,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,7 +156,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FF005071"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -204,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -216,6 +208,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF005071"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -529,37 +526,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -568,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -595,7 +592,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
